--- a/Assets/ArtRes/Excel/关卡表.xlsx
+++ b/Assets/ArtRes/Excel/关卡表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_Project\weiqi4\Assets\ArtRes\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247506CA-ED50-496C-AA33-277E9FAF2037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5BED82-FDD5-41D8-BD76-B1FB9E23B725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -603,14 +603,14 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -3312,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="H70" s="12">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I70" s="14">
         <v>2147483647</v>
@@ -3347,7 +3347,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="12">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I71" s="14">
         <v>2147483647</v>
@@ -3382,7 +3382,7 @@
         <v>1</v>
       </c>
       <c r="H72" s="12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I72" s="14">
         <v>2147483647</v>
@@ -3417,7 +3417,7 @@
         <v>1</v>
       </c>
       <c r="H73" s="12">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I73" s="14">
         <v>2147483647</v>
@@ -3452,7 +3452,7 @@
         <v>1</v>
       </c>
       <c r="H74" s="12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I74" s="14">
         <v>2147483647</v>
@@ -3487,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="12">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I75" s="14">
         <v>2147483647</v>
